--- a/combine_harvest_abstract/deliverables/31-47N-76W/47N-76W-31_Johnson_Co_Penterra_Abstract_Index.xlsx
+++ b/combine_harvest_abstract/deliverables/31-47N-76W/47N-76W-31_Johnson_Co_Penterra_Abstract_Index.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qualifications" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Qualifications" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Index'!$1:$9</definedName>
@@ -127,7 +127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -199,6 +199,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -659,10 +662,10 @@
           <t>0084-0029</t>
         </is>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>18751</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="25" t="n">
         <v>18765</v>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -698,10 +701,10 @@
           <t>RW32-0623-0632</t>
         </is>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="25" t="n">
         <v>43087</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="25" t="n">
         <v>43210</v>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -742,7 +745,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="25" t="n">
         <v>44207</v>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -778,10 +781,10 @@
           <t>0405-0049</t>
         </is>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="25" t="n">
         <v>45555</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="25" t="n">
         <v>45594</v>
       </c>
       <c r="H13" s="20" t="inlineStr">
